--- a/nrf/nrf.xlsx
+++ b/nrf/nrf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\nrf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEBA58F9-EF8E-4A17-A8B0-79482DA41713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F207874-2EA8-4048-9D62-491AFA9B9D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6CDA5250-8EE7-481F-B63B-0578963594DA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{11D12471-054B-4068-925A-731467A3FD47}"/>
   </bookViews>
   <sheets>
     <sheet name="nrf" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="131">
   <si>
     <t>Comment</t>
   </si>
@@ -125,7 +125,7 @@
     <t>100nF</t>
   </si>
   <si>
-    <t>Capacitor MLCC 0603 100nF 50V</t>
+    <t>Capacitor MLCC 0603 100nF 50V | AVX 06035C104K4T2A</t>
   </si>
   <si>
     <t>C13</t>
@@ -188,204 +188,207 @@
     <t>SMA</t>
   </si>
   <si>
+    <t>FIDUCIAL_1MM</t>
+  </si>
+  <si>
+    <t>Fiducial Alignment Points   Various fiducial points for machine vision alignment.</t>
+  </si>
+  <si>
+    <t>FID1, FID2</t>
+  </si>
+  <si>
+    <t>MTSW-103-13-G-S-570</t>
+  </si>
+  <si>
+    <t>Connector Header Through Hole 3 position 0.100 (2.54mm)</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>SAMTEC_MTSW-103-13-G-S-570</t>
+  </si>
+  <si>
+    <t>TYPE-C-31-M-12</t>
+  </si>
+  <si>
+    <t>USB Connectors 24 Receptacle 1 8.94*7.3mm RoHS</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>HRO_TYPE-C-31-M-12</t>
+  </si>
+  <si>
+    <t>10nH</t>
+  </si>
+  <si>
+    <t>FIXED IND 10NH 600MA 100 MOHM</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>INDC2015X152N</t>
+  </si>
+  <si>
+    <t>LQW2BAS10NG00L</t>
+  </si>
+  <si>
+    <t>22uH</t>
+  </si>
+  <si>
+    <t>Inductor with Inductance: 22uH Tol. +/-20%, Package: 0805 (2012)</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>INDC2012X145N</t>
+  </si>
+  <si>
+    <t>LQM21DH220M70L</t>
+  </si>
+  <si>
+    <t>AO3401</t>
+  </si>
+  <si>
+    <t>P-Channel 30 V 4A (Ta) 1.4W (Ta) Surface Mount SOT-23-3</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>SOT23-3</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>0201 anti-sulfurated resistor 0603 Anti-Sulfurated</t>
+  </si>
+  <si>
+    <t>R1, R2, R3, R24</t>
+  </si>
+  <si>
+    <t>RES_ERJU03J5R6V</t>
+  </si>
+  <si>
+    <t>ERJU03J5R6V</t>
+  </si>
+  <si>
+    <t>4K7</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>22R</t>
+  </si>
+  <si>
+    <t>R10, R11</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>R12, R13, R14, R15</t>
+  </si>
+  <si>
+    <t>5K1</t>
+  </si>
+  <si>
+    <t>R16, R17</t>
+  </si>
+  <si>
+    <t>43K</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>6.2K</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>15K</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>4.7K</t>
+  </si>
+  <si>
+    <t>R22, R23</t>
+  </si>
+  <si>
+    <t>SK12D07VG4</t>
+  </si>
+  <si>
+    <t>Switch Slide ON ON SPDT Side Slide 0.3A 30VDC PC Pins Bracket Mount/Through Hole Bulk</t>
+  </si>
+  <si>
+    <t>SW2</t>
+  </si>
+  <si>
+    <t>MDBT50Q-1MV2</t>
+  </si>
+  <si>
+    <t>802.15.4, Bluetooth Bluetooth v5.4, ZigbeeÂ® Transceiver Module 2.36GHz ~ 2.5GHz Integrated, Chip Surface Mount</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>XCVR_MDBT50Q-1MV2</t>
+  </si>
+  <si>
+    <t>RT9080-33GJ5</t>
+  </si>
+  <si>
+    <t>Linear Voltage Regulator IC Positive Fixed 1 Output 600mA TSOT-23-5</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>SOT94P280X100-5N</t>
+  </si>
+  <si>
+    <t>MCP73831T-2ACI/OT</t>
+  </si>
+  <si>
+    <t>MCP73831/2 LIPO Charger    VDD: 3.75 - 6V  Temp -40 - 85Â°C  Programmable Charge Rate: 15-500mA       NOTE: STAT is a tri-state logic output on the MCP73831 and an open-drain output on the MCP73832.   SOT23-5 with 4.2V output and tri-state logic on STAT = MCP73831T-2ACI/OT</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>SOT23-5</t>
+  </si>
+  <si>
+    <t>MCP73831/2</t>
+  </si>
+  <si>
+    <t>GY-BNO055</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Designator45, Designator53</t>
-  </si>
-  <si>
-    <t>PCBComponent_1</t>
-  </si>
-  <si>
-    <t>MTSW-103-13-G-S-570</t>
-  </si>
-  <si>
-    <t>Connector Header Through Hole 3 position 0.100 (2.54mm)</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>SAMTEC_MTSW-103-13-G-S-570</t>
-  </si>
-  <si>
-    <t>TYPE-C-31-M-12</t>
-  </si>
-  <si>
-    <t>USB Connectors 24 Receptacle 1 8.94*7.3mm RoHS</t>
-  </si>
-  <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>HRO_TYPE-C-31-M-12</t>
-  </si>
-  <si>
-    <t>10nH</t>
-  </si>
-  <si>
-    <t>FIXED IND 10NH 600MA 100 MOHM</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>INDC2015X152N</t>
-  </si>
-  <si>
-    <t>LQW2BAS10NG00L</t>
-  </si>
-  <si>
-    <t>22uH</t>
-  </si>
-  <si>
-    <t>Inductor with Inductance: 22uH Tol. +/-20%, Package: 0805 (2012)</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>INDC2012X145N</t>
-  </si>
-  <si>
-    <t>LQM21DH220M70L</t>
-  </si>
-  <si>
-    <t>AO3401</t>
-  </si>
-  <si>
-    <t>P-Channel 30 V 4A (Ta) 1.4W (Ta) Surface Mount SOT-23-3</t>
-  </si>
-  <si>
-    <t>Q3</t>
-  </si>
-  <si>
-    <t>SOT23-3</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>0201 anti-sulfurated resistor 0603 Anti-Sulfurated</t>
-  </si>
-  <si>
-    <t>R1, R2, R3, R24</t>
-  </si>
-  <si>
-    <t>RES_ERJU03J5R6V</t>
-  </si>
-  <si>
-    <t>ERJU03J5R6V</t>
-  </si>
-  <si>
-    <t>4K7</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>22R</t>
-  </si>
-  <si>
-    <t>R10, R11</t>
-  </si>
-  <si>
-    <t>100K</t>
-  </si>
-  <si>
-    <t>R12, R13, R14, R15</t>
-  </si>
-  <si>
-    <t>5K1</t>
-  </si>
-  <si>
-    <t>R16, R17</t>
-  </si>
-  <si>
-    <t>43K</t>
-  </si>
-  <si>
-    <t>R18</t>
-  </si>
-  <si>
-    <t>6.2K</t>
-  </si>
-  <si>
-    <t>R19</t>
-  </si>
-  <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>15K</t>
-  </si>
-  <si>
-    <t>R21</t>
-  </si>
-  <si>
-    <t>4.7K</t>
-  </si>
-  <si>
-    <t>R22, R23</t>
-  </si>
-  <si>
-    <t>RKB2</t>
-  </si>
-  <si>
-    <t>SMT Tact Switches RKB2 https://www.digikey.com/short/m027prz5</t>
-  </si>
-  <si>
-    <t>SW1, SW2</t>
-  </si>
-  <si>
-    <t>BTN_RKB2_4.6X2.8</t>
-  </si>
-  <si>
-    <t>SWITCH_TACT_SMT_RKB2</t>
-  </si>
-  <si>
-    <t>MDBT50Q-1MV2</t>
-  </si>
-  <si>
-    <t>802.15.4, Bluetooth Bluetooth v5.4, ZigbeeÂ® Transceiver Module 2.36GHz ~ 2.5GHz Integrated, Chip Surface Mount</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>XCVR_MDBT50Q-1MV2</t>
-  </si>
-  <si>
-    <t>RT9080-33GJ5</t>
-  </si>
-  <si>
-    <t>Linear Voltage Regulator IC Positive Fixed 1 Output 600mA TSOT-23-5</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>SOT94P280X100-5N</t>
-  </si>
-  <si>
-    <t>MCP73831T-2ACI/OT</t>
-  </si>
-  <si>
-    <t>MCP73831/2 LIPO Charger    VDD: 3.75 - 6V  Temp -40 - 85Â°C  Programmable Charge Rate: 15-500mA       NOTE: STAT is a tri-state logic output on the MCP73831 and an open-drain output on the MCP73832.   SOT23-5 with 4.2V output and tri-state logic on STAT = MCP73831T-2ACI/OT</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>SOT23-5</t>
-  </si>
-  <si>
-    <t>MCP73831/2</t>
-  </si>
-  <si>
     <t>MT3608</t>
   </si>
   <si>
@@ -398,19 +401,13 @@
     <t>SOT95P280X145-6N</t>
   </si>
   <si>
-    <t>2x5 0.05"</t>
-  </si>
-  <si>
-    <t>Serial Wire (SW-DP) Connector   Standard 0.05" 10-pin connector is for use with the Cortex M and Cortex A SWD (serial wire debugger) interface (SW-DP)Connectors 2x05_1.27MM_SMT - Inexpensive surface-mount header with bare pins, compatible with standard 10-pin SWD cables (4UCON: 16846)  2x05_1.27MM_BOX_NOPOSTS - Polarised surface-mount box (4UCON with caps: 19735, without caps: 15117  2x05_1.27MM_BOX_POSTS - Polarised surface-mount box with mounting holes (4UCON: 20317)    Pinout: http://infocenter.arm.com/help/topic/com.arm.doc.faqs/attached/13634/cortex_debug_connectors.pdf  http://www.keil.com/peripherals/coresight/connectors.asp</t>
+    <t>FTSH-105-01-X-DV-P-K-X</t>
   </si>
   <si>
     <t>X2</t>
   </si>
   <si>
-    <t>2X05_1.27MM_BOX_POSTS</t>
-  </si>
-  <si>
-    <t>JTAG-CORTEXBOXPOSTS</t>
+    <t>SAMTEC_FTSH-105-01-X-DV-P-K-X</t>
   </si>
   <si>
     <t>S2B-PH-SM4-TB</t>
@@ -833,8 +830,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018AD427-9238-4103-BC6D-9BCD0310578E}">
-  <dimension ref="A1:F35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13557C01-9A50-4E2E-9A28-D0F961D1B71D}">
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="19.7109375" customWidth="1"/>
@@ -1062,16 +1059,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>48</v>
@@ -1391,30 +1388,30 @@
         <v>98</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F29" s="1">
         <v>1</v>
@@ -1422,19 +1419,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="E30" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F30" s="1">
         <v>1</v>
@@ -1442,19 +1439,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="F31" s="1">
         <v>1</v>
@@ -1462,19 +1459,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F32" s="1">
         <v>1</v>
@@ -1482,19 +1479,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F33" s="1">
         <v>1</v>
@@ -1502,19 +1499,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F34" s="1">
         <v>1</v>
@@ -1522,21 +1519,41 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F35" s="1">
+      <c r="F36" s="1">
         <v>1</v>
       </c>
     </row>
